--- a/data/company-pool/公司.xlsx
+++ b/data/company-pool/公司.xlsx
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L727"/>
+  <dimension ref="A1:L744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,7 +945,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1003,7 +1002,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1061,7 +1059,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1119,7 +1116,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1177,7 +1173,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1235,7 +1230,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1293,7 +1287,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1351,7 +1344,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1409,7 +1401,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1467,7 +1458,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1525,7 +1515,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1583,7 +1572,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1641,7 +1629,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1699,7 +1686,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1757,7 +1743,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1815,7 +1800,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1873,7 +1857,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1931,7 +1914,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1989,7 +1971,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2047,7 +2028,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2105,7 +2085,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2163,7 +2142,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2221,7 +2199,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2279,7 +2256,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2337,7 +2313,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2395,7 +2370,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2453,7 +2427,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2511,7 +2484,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2569,7 +2541,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2627,7 +2598,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2685,7 +2655,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2743,7 +2712,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2801,7 +2769,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2859,7 +2826,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2917,7 +2883,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2975,7 +2940,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3033,7 +2997,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3091,7 +3054,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3149,7 +3111,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3207,7 +3168,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3265,7 +3225,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3323,7 +3282,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3381,7 +3339,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3439,7 +3396,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3497,7 +3453,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3555,7 +3510,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3613,7 +3567,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3671,7 +3624,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3729,7 +3681,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3787,7 +3738,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3845,7 +3795,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3903,7 +3852,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3961,7 +3909,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4019,7 +3966,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4077,7 +4023,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4135,7 +4080,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4193,7 +4137,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4251,7 +4194,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4309,7 +4251,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4367,7 +4308,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4425,7 +4365,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4483,7 +4422,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4541,7 +4479,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4599,7 +4536,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4657,7 +4593,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4715,7 +4650,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4773,7 +4707,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4831,7 +4764,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4889,7 +4821,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4947,7 +4878,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5005,7 +4935,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5063,7 +4992,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5121,7 +5049,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5179,7 +5106,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5237,7 +5163,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5295,7 +5220,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5353,7 +5277,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5411,7 +5334,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5469,7 +5391,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5527,7 +5448,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5585,7 +5505,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5643,7 +5562,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5701,7 +5619,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5759,7 +5676,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5817,7 +5733,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5875,7 +5790,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5933,7 +5847,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5991,7 +5904,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6049,7 +5961,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6107,7 +6018,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6165,7 +6075,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6223,7 +6132,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6281,7 +6189,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6339,7 +6246,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6397,7 +6303,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6455,7 +6360,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6513,7 +6417,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6571,7 +6474,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6629,7 +6531,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6687,7 +6588,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6745,7 +6645,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6803,7 +6702,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6861,7 +6759,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6919,7 +6816,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6977,7 +6873,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7035,7 +6930,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7093,7 +6987,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7151,7 +7044,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7209,7 +7101,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7267,7 +7158,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7325,7 +7215,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7383,7 +7272,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7441,7 +7329,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7499,7 +7386,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7557,7 +7443,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7615,7 +7500,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7673,7 +7557,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7731,7 +7614,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7789,7 +7671,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7847,7 +7728,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7905,7 +7785,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7963,7 +7842,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8021,7 +7899,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8079,7 +7956,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8137,7 +8013,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8195,7 +8070,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8253,7 +8127,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8311,7 +8184,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8369,7 +8241,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8427,7 +8298,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8485,7 +8355,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8543,7 +8412,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8601,7 +8469,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8659,7 +8526,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8717,7 +8583,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8775,7 +8640,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8833,7 +8697,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8891,7 +8754,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8949,7 +8811,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9007,7 +8868,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9065,7 +8925,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9123,7 +8982,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9181,7 +9039,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9239,7 +9096,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9297,7 +9153,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9355,7 +9210,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9413,7 +9267,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9471,7 +9324,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9529,7 +9381,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9587,7 +9438,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9645,7 +9495,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9703,7 +9552,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9761,7 +9609,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9819,7 +9666,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9877,7 +9723,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9935,7 +9780,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9993,7 +9837,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10051,7 +9894,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10109,7 +9951,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10167,7 +10008,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10225,7 +10065,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10283,7 +10122,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10328,7 +10166,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>PCB-2026-002</t>
+          <t>PCB-2026-002;GLASS-2026-001</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10341,7 +10179,11 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>nan；PLP2000板级曝光首台量产订单(688630)，先进封装新增长线</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10399,7 +10241,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10457,7 +10298,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10515,7 +10355,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10573,7 +10412,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10631,7 +10469,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10689,7 +10526,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10747,7 +10583,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10805,7 +10640,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10863,7 +10697,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10921,7 +10754,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10979,7 +10811,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11037,7 +10868,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11095,7 +10925,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11153,7 +10982,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11211,7 +11039,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11269,7 +11096,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11327,7 +11153,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11385,7 +11210,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11443,7 +11267,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11501,7 +11324,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11559,7 +11381,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11617,7 +11438,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11675,7 +11495,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11733,7 +11552,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11791,7 +11609,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11849,7 +11666,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11907,7 +11723,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11965,7 +11780,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12023,7 +11837,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12081,7 +11894,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12139,7 +11951,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12197,7 +12008,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12255,7 +12065,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12313,7 +12122,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12371,7 +12179,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12429,7 +12236,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12487,7 +12293,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12545,7 +12350,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12603,7 +12407,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12661,7 +12464,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12719,7 +12521,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12777,7 +12578,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12835,7 +12635,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12893,7 +12692,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12951,7 +12749,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13009,7 +12806,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13067,7 +12863,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13125,7 +12920,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13183,7 +12977,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13241,7 +13034,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13299,7 +13091,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13357,7 +13148,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13415,7 +13205,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13473,7 +13262,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13531,7 +13319,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13589,7 +13376,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13647,7 +13433,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13705,7 +13490,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13763,7 +13547,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13821,7 +13604,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13879,7 +13661,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13937,7 +13718,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13995,7 +13775,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14053,7 +13832,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -14111,7 +13889,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14169,7 +13946,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14227,7 +14003,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14285,7 +14060,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14343,7 +14117,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14401,7 +14174,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14459,7 +14231,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14517,7 +14288,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14575,7 +14345,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14633,7 +14402,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14691,7 +14459,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14749,7 +14516,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14807,7 +14573,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14865,7 +14630,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14923,7 +14687,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14981,7 +14744,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -15039,7 +14801,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -15097,7 +14858,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -15155,7 +14915,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -15213,7 +14972,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -15271,7 +15029,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -15329,7 +15086,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -15387,7 +15143,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -15445,7 +15200,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -15503,7 +15257,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -15561,7 +15314,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -15619,7 +15371,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15677,7 +15428,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15735,7 +15485,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15793,7 +15542,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15851,7 +15599,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15909,7 +15656,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15967,7 +15713,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -16025,7 +15770,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -16083,7 +15827,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -16141,7 +15884,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -16199,7 +15941,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -16257,7 +15998,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -16315,7 +16055,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -16373,7 +16112,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -16431,7 +16169,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -16489,7 +16226,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -16547,7 +16283,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16605,7 +16340,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16663,7 +16397,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16721,7 +16454,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16779,7 +16511,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16837,7 +16568,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16895,7 +16625,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16953,7 +16682,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -17011,7 +16739,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -17069,7 +16796,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -17127,7 +16853,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -17185,7 +16910,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -17243,7 +16967,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -17301,7 +17024,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -17359,7 +17081,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -17417,7 +17138,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -17475,7 +17195,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -17533,7 +17252,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -17591,7 +17309,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -17649,7 +17366,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -17707,7 +17423,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -17765,7 +17480,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -17823,7 +17537,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -17881,7 +17594,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -17939,7 +17651,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -17997,7 +17708,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -18055,7 +17765,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -18113,7 +17822,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -18171,7 +17879,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -18229,7 +17936,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -18287,7 +17993,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -18345,7 +18050,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -18403,7 +18107,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -18461,7 +18164,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -18519,7 +18221,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -18577,7 +18278,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -18635,7 +18335,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -18693,7 +18392,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -18751,7 +18449,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -18809,7 +18506,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -18867,7 +18563,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -18925,7 +18620,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -18983,7 +18677,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -19041,7 +18734,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -19099,7 +18791,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -19157,7 +18848,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -19215,7 +18905,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -19273,7 +18962,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -19331,7 +19019,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -19389,7 +19076,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -19447,7 +19133,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -19505,7 +19190,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -19563,7 +19247,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -19621,7 +19304,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -19679,7 +19361,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -19737,7 +19418,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -19795,7 +19475,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -19853,7 +19532,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -19911,7 +19589,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -19969,7 +19646,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -20027,7 +19703,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -20085,7 +19760,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -20143,7 +19817,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -20201,7 +19874,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -20259,7 +19931,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -20317,7 +19988,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -20375,7 +20045,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -20433,7 +20102,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -20491,7 +20159,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -20611,7 +20278,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -20669,7 +20335,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -20727,7 +20392,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -20785,7 +20449,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -20843,7 +20506,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -20901,7 +20563,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -20959,7 +20620,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -21017,7 +20677,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -21075,7 +20734,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -21133,7 +20791,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -21191,7 +20848,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -21249,7 +20905,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -21307,7 +20962,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -21365,7 +21019,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -21423,7 +21076,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -21481,7 +21133,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -21539,7 +21190,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -21597,7 +21247,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -21655,7 +21304,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -21713,7 +21361,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -21771,7 +21418,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -21829,7 +21475,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -21887,7 +21532,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -21945,7 +21589,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -22003,7 +21646,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -22061,7 +21703,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -22119,7 +21760,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -22177,7 +21817,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -22235,7 +21874,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -22293,7 +21931,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -22351,7 +21988,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -22409,7 +22045,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -22467,7 +22102,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -22525,7 +22159,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -22583,7 +22216,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -22641,7 +22273,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -22699,7 +22330,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -22757,7 +22387,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -22815,7 +22444,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -22873,7 +22501,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -22931,7 +22558,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -22989,7 +22615,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -23047,7 +22672,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -23105,7 +22729,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -23163,7 +22786,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -23221,7 +22843,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -23279,7 +22900,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -23337,7 +22957,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -23380,7 +22999,6 @@
           <t>今日增补</t>
         </is>
       </c>
-      <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr">
         <is>
           <t>mapping</t>
@@ -23453,7 +23071,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -23511,7 +23128,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -23569,7 +23185,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -23627,7 +23242,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -23685,7 +23299,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -23743,7 +23356,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -23801,7 +23413,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -23859,7 +23470,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -23917,7 +23527,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -23975,7 +23584,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -24033,7 +23641,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -24091,7 +23698,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -24149,7 +23755,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -24207,7 +23812,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -24265,7 +23869,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -24323,7 +23926,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -24381,7 +23983,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -24439,7 +24040,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -24497,7 +24097,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -24555,7 +24154,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -24613,7 +24211,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -24671,7 +24268,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -24729,7 +24325,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -24787,7 +24382,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -24845,7 +24439,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -24903,7 +24496,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -24961,7 +24553,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -25019,7 +24610,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -25077,7 +24667,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -25135,7 +24724,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -25193,7 +24781,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -25251,7 +24838,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -25309,7 +24895,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -25367,7 +24952,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -25425,7 +25009,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -25483,7 +25066,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -25541,7 +25123,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -25599,7 +25180,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -25657,7 +25237,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -25715,7 +25294,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -25773,7 +25351,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -25831,7 +25408,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -25889,7 +25465,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -25947,7 +25522,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -26005,7 +25579,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -26063,7 +25636,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -26121,7 +25693,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -26179,7 +25750,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -26237,7 +25807,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -26295,7 +25864,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -26353,7 +25921,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -26411,7 +25978,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -26469,7 +26035,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -26527,7 +26092,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -26585,7 +26149,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -26643,7 +26206,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -26701,7 +26263,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -26759,7 +26320,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -26817,7 +26377,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -26875,7 +26434,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -26933,7 +26491,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -26991,7 +26548,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -27049,7 +26605,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -27107,7 +26662,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -27165,7 +26719,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -27223,7 +26776,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -27281,7 +26833,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -27339,7 +26890,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -27397,7 +26947,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -27455,7 +27004,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -27513,7 +27061,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -27571,7 +27118,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -27629,7 +27175,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -27687,7 +27232,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -27745,7 +27289,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -27803,7 +27346,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -27861,7 +27403,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -27919,7 +27460,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -27977,7 +27517,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -28035,7 +27574,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -28093,7 +27631,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -28151,7 +27688,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -28209,7 +27745,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -28267,7 +27802,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -28325,7 +27859,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -28383,7 +27916,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -28441,7 +27973,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -28499,7 +28030,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -28557,7 +28087,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -28615,7 +28144,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -28673,7 +28201,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -28731,7 +28258,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -28789,7 +28315,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -28847,7 +28372,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -28905,7 +28429,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -28963,7 +28486,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -29021,7 +28543,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -29079,7 +28600,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -29137,7 +28657,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -29195,7 +28714,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -29253,7 +28771,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -29311,7 +28828,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -29369,7 +28885,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -29427,7 +28942,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -29485,7 +28999,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -29543,7 +29056,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -29601,7 +29113,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -29659,7 +29170,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -29717,7 +29227,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -29775,7 +29284,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -29833,7 +29341,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -29891,7 +29398,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -29949,7 +29455,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -30007,7 +29512,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -30065,7 +29569,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -30123,7 +29626,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -30181,7 +29683,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -30239,7 +29740,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -30297,7 +29797,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -30355,7 +29854,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -30413,7 +29911,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -30471,7 +29968,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -30529,7 +30025,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -30587,7 +30082,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -30645,7 +30139,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -30703,7 +30196,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -30761,7 +30253,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -30819,7 +30310,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -30877,7 +30367,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -30935,7 +30424,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -30993,7 +30481,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -31051,7 +30538,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -31109,7 +30595,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -31167,7 +30652,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -31225,7 +30709,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -31283,7 +30766,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -31341,7 +30823,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -31399,7 +30880,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -31457,7 +30937,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -31515,7 +30994,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -31573,7 +31051,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -31631,7 +31108,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -31689,7 +31165,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -31747,7 +31222,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -31805,7 +31279,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -31863,7 +31336,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -31921,7 +31393,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -31979,7 +31450,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -32037,7 +31507,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -32095,7 +31564,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -32153,7 +31621,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -32211,7 +31678,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -32269,7 +31735,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -32327,7 +31792,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -32385,7 +31849,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -32443,7 +31906,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -32501,7 +31963,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -32559,7 +32020,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -32617,7 +32077,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -32675,7 +32134,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -32733,7 +32191,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -32791,7 +32248,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -32849,7 +32305,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -32907,7 +32362,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -32965,7 +32419,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -33023,7 +32476,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -33081,7 +32533,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -33139,7 +32590,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -33197,7 +32647,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -33255,7 +32704,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -33313,7 +32761,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -33371,7 +32818,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -33429,7 +32875,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -33487,7 +32932,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -33545,7 +32989,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -33603,7 +33046,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -33661,7 +33103,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -33719,7 +33160,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -33777,7 +33217,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -33835,7 +33274,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -33893,7 +33331,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -33951,7 +33388,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -34009,7 +33445,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -34067,7 +33502,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -34125,7 +33559,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -34183,7 +33616,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -34241,7 +33673,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -34299,7 +33730,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -34357,7 +33787,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -34415,7 +33844,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -34473,7 +33901,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -34531,7 +33958,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -34589,7 +34015,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -34647,7 +34072,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -34705,7 +34129,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -34763,7 +34186,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -34821,7 +34243,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -34879,7 +34300,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -34937,7 +34357,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -34995,7 +34414,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -35053,7 +34471,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -35111,7 +34528,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -35169,7 +34585,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -35227,7 +34642,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -35285,7 +34699,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -35343,7 +34756,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -35401,7 +34813,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -35459,7 +34870,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -35517,7 +34927,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -35575,7 +34984,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -35633,7 +35041,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -35691,7 +35098,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -35749,7 +35155,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -35807,7 +35212,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -35865,7 +35269,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -35923,7 +35326,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -35981,7 +35383,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -36039,7 +35440,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -36097,7 +35497,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -36155,7 +35554,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -36213,7 +35611,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -36271,7 +35668,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -36329,7 +35725,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -36387,7 +35782,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -36445,7 +35839,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -36503,7 +35896,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -36561,7 +35953,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -36619,7 +36010,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -36677,7 +36067,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -36735,7 +36124,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -36793,7 +36181,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -36851,7 +36238,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -36909,7 +36295,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -36967,7 +36352,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -37025,7 +36409,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -37083,7 +36466,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -37141,7 +36523,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -37199,7 +36580,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -37257,7 +36637,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -37315,7 +36694,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -37373,7 +36751,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -37431,7 +36808,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -37489,7 +36865,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -37547,7 +36922,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -37605,7 +36979,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -37663,7 +37036,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -37721,7 +37093,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -37779,7 +37150,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -37837,7 +37207,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -37895,7 +37264,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -37953,7 +37321,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -38011,7 +37378,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -38069,7 +37435,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -38127,7 +37492,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -38185,7 +37549,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -38243,7 +37606,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -38301,7 +37663,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -38359,7 +37720,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -38417,7 +37777,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -38475,7 +37834,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -38533,7 +37891,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -38591,7 +37948,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -38649,7 +38005,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -38707,7 +38062,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -38765,7 +38119,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -38823,7 +38176,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -38881,7 +38233,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -38899,7 +38250,6 @@
           <t>HBM产业链</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr"/>
       <c r="E657" t="inlineStr">
         <is>
           <t>深科技</t>
@@ -38920,7 +38270,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I657" t="inlineStr"/>
       <c r="J657" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -38953,7 +38302,6 @@
           <t>电网/特高压</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr"/>
       <c r="E658" t="inlineStr">
         <is>
           <t>许继电气</t>
@@ -38974,7 +38322,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I658" t="inlineStr"/>
       <c r="J658" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39007,7 +38354,6 @@
           <t>先进封装</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr">
         <is>
           <t>振华科技</t>
@@ -39028,7 +38374,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I659" t="inlineStr"/>
       <c r="J659" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39061,7 +38406,6 @@
           <t>核电/SMR</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr">
         <is>
           <t>中核科技</t>
@@ -39082,7 +38426,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I660" t="inlineStr"/>
       <c r="J660" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39115,7 +38458,6 @@
           <t>人形机器人零部件</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr">
         <is>
           <t>秦川机床</t>
@@ -39136,7 +38478,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I661" t="inlineStr"/>
       <c r="J661" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39169,7 +38510,6 @@
           <t>FPGA</t>
         </is>
       </c>
-      <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr">
         <is>
           <t>紫光国芯</t>
@@ -39190,7 +38530,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I662" t="inlineStr"/>
       <c r="J662" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39223,7 +38562,6 @@
           <t>晶圆材料</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr"/>
       <c r="E663" t="inlineStr">
         <is>
           <t>苏州固锝</t>
@@ -39244,7 +38582,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I663" t="inlineStr"/>
       <c r="J663" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39277,7 +38614,6 @@
           <t>网络/连接器</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr"/>
       <c r="E664" t="inlineStr">
         <is>
           <t>沃尔核材</t>
@@ -39298,7 +38634,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I664" t="inlineStr"/>
       <c r="J664" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39331,7 +38666,6 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr">
         <is>
           <t>科大讯飞</t>
@@ -39352,7 +38686,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I665" t="inlineStr"/>
       <c r="J665" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39385,7 +38718,6 @@
           <t>卫星互联网</t>
         </is>
       </c>
-      <c r="D666" t="inlineStr"/>
       <c r="E666" t="inlineStr">
         <is>
           <t>海格通信</t>
@@ -39406,7 +38738,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I666" t="inlineStr"/>
       <c r="J666" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39439,7 +38770,6 @@
           <t>人形机器人零部件</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr"/>
       <c r="E667" t="inlineStr">
         <is>
           <t>双环传动</t>
@@ -39460,7 +38790,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I667" t="inlineStr"/>
       <c r="J667" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39493,7 +38822,6 @@
           <t>网络/连接器</t>
         </is>
       </c>
-      <c r="D668" t="inlineStr"/>
       <c r="E668" t="inlineStr">
         <is>
           <t>立讯精密</t>
@@ -39514,7 +38842,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I668" t="inlineStr"/>
       <c r="J668" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39547,7 +38874,6 @@
           <t>整机/本体</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr"/>
       <c r="E669" t="inlineStr">
         <is>
           <t>埃斯顿</t>
@@ -39568,7 +38894,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I669" t="inlineStr"/>
       <c r="J669" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39601,7 +38926,6 @@
           <t>工业机器人</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr"/>
       <c r="E670" t="inlineStr">
         <is>
           <t>机器人</t>
@@ -39622,7 +38946,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I670" t="inlineStr"/>
       <c r="J670" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39655,7 +38978,6 @@
           <t>人形机器人零部件</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr"/>
       <c r="E671" t="inlineStr">
         <is>
           <t>汇川技术</t>
@@ -39676,7 +38998,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I671" t="inlineStr"/>
       <c r="J671" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39709,7 +39030,6 @@
           <t>数控机床</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr">
         <is>
           <t>华中数控</t>
@@ -39730,7 +39050,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I672" t="inlineStr"/>
       <c r="J672" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39763,7 +39082,6 @@
           <t>湿电子化学品</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr">
         <is>
           <t>上海新阳</t>
@@ -39784,7 +39102,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I673" t="inlineStr"/>
       <c r="J673" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39817,7 +39134,6 @@
           <t>人形机器人零部件</t>
         </is>
       </c>
-      <c r="D674" t="inlineStr"/>
       <c r="E674" t="inlineStr">
         <is>
           <t>精锻科技</t>
@@ -39838,7 +39154,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I674" t="inlineStr"/>
       <c r="J674" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39933,7 +39248,6 @@
           <t>逻辑芯片</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr"/>
       <c r="E676" t="inlineStr">
         <is>
           <t>景嘉微</t>
@@ -39954,7 +39268,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I676" t="inlineStr"/>
       <c r="J676" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -39987,7 +39300,6 @@
           <t>UPS/液冷</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr"/>
       <c r="E677" t="inlineStr">
         <is>
           <t>高澜股份</t>
@@ -40008,7 +39320,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I677" t="inlineStr"/>
       <c r="J677" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40041,7 +39352,6 @@
           <t>晶圆材料</t>
         </is>
       </c>
-      <c r="D678" t="inlineStr"/>
       <c r="E678" t="inlineStr">
         <is>
           <t>立昂技术</t>
@@ -40062,7 +39372,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I678" t="inlineStr"/>
       <c r="J678" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40095,7 +39404,6 @@
           <t>工业机器人</t>
         </is>
       </c>
-      <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr">
         <is>
           <t>拓斯达</t>
@@ -40116,7 +39424,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I679" t="inlineStr"/>
       <c r="J679" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40149,7 +39456,6 @@
           <t>人形机器人零部件</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr"/>
       <c r="E680" t="inlineStr">
         <is>
           <t>江苏雷利</t>
@@ -40170,7 +39476,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I680" t="inlineStr"/>
       <c r="J680" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40203,7 +39508,6 @@
           <t>人形机器人零部件</t>
         </is>
       </c>
-      <c r="D681" t="inlineStr"/>
       <c r="E681" t="inlineStr">
         <is>
           <t>精研科技</t>
@@ -40224,7 +39528,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I681" t="inlineStr"/>
       <c r="J681" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40257,7 +39560,6 @@
           <t>模拟芯片</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr">
         <is>
           <t>卓胜微</t>
@@ -40278,7 +39580,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I682" t="inlineStr"/>
       <c r="J682" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40311,7 +39612,6 @@
           <t>机器视觉</t>
         </is>
       </c>
-      <c r="D683" t="inlineStr"/>
       <c r="E683" t="inlineStr">
         <is>
           <t>矩子科技</t>
@@ -40332,7 +39632,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I683" t="inlineStr"/>
       <c r="J683" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40365,7 +39664,6 @@
           <t>存储/HBM</t>
         </is>
       </c>
-      <c r="D684" t="inlineStr"/>
       <c r="E684" t="inlineStr">
         <is>
           <t>江波龙</t>
@@ -40386,7 +39684,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I684" t="inlineStr"/>
       <c r="J684" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40419,7 +39716,6 @@
           <t>电网/特高压</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr"/>
       <c r="E685" t="inlineStr">
         <is>
           <t>特变电工</t>
@@ -40440,7 +39736,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I685" t="inlineStr"/>
       <c r="J685" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40473,7 +39768,6 @@
           <t>卫星互联网</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr"/>
       <c r="E686" t="inlineStr">
         <is>
           <t>中国卫星</t>
@@ -40494,7 +39788,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I686" t="inlineStr"/>
       <c r="J686" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40527,7 +39820,6 @@
           <t>电网/特高压</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr"/>
       <c r="E687" t="inlineStr">
         <is>
           <t>平高电气</t>
@@ -40548,7 +39840,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I687" t="inlineStr"/>
       <c r="J687" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40581,7 +39872,6 @@
           <t>SiC/GaN</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr"/>
       <c r="E688" t="inlineStr">
         <is>
           <t>闻泰科技</t>
@@ -40602,7 +39892,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I688" t="inlineStr"/>
       <c r="J688" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40635,7 +39924,6 @@
           <t>电网/特高压</t>
         </is>
       </c>
-      <c r="D689" t="inlineStr"/>
       <c r="E689" t="inlineStr">
         <is>
           <t>国电南瑞</t>
@@ -40656,7 +39944,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I689" t="inlineStr"/>
       <c r="J689" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40689,7 +39976,6 @@
           <t>AI基础设施</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr">
         <is>
           <t>工业富联</t>
@@ -40710,7 +39996,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I690" t="inlineStr"/>
       <c r="J690" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40743,7 +40028,6 @@
           <t>卫星互联网</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr"/>
       <c r="E691" t="inlineStr">
         <is>
           <t>中国卫通</t>
@@ -40764,7 +40048,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I691" t="inlineStr"/>
       <c r="J691" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40797,7 +40080,6 @@
           <t>AI基础设施</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr"/>
       <c r="E692" t="inlineStr">
         <is>
           <t>中科曙光</t>
@@ -40818,7 +40100,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I692" t="inlineStr"/>
       <c r="J692" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40851,7 +40132,6 @@
           <t>精密零部件</t>
         </is>
       </c>
-      <c r="D693" t="inlineStr"/>
       <c r="E693" t="inlineStr">
         <is>
           <t>新莱应材</t>
@@ -40872,7 +40152,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I693" t="inlineStr"/>
       <c r="J693" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40905,7 +40184,6 @@
           <t>石英</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr"/>
       <c r="E694" t="inlineStr">
         <is>
           <t>石英股份</t>
@@ -40926,7 +40204,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I694" t="inlineStr"/>
       <c r="J694" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -40959,7 +40236,6 @@
           <t>模拟芯片</t>
         </is>
       </c>
-      <c r="D695" t="inlineStr"/>
       <c r="E695" t="inlineStr">
         <is>
           <t>韦尔股份</t>
@@ -40980,7 +40256,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I695" t="inlineStr"/>
       <c r="J695" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41013,7 +40288,6 @@
           <t>刻蚀/CVD设备</t>
         </is>
       </c>
-      <c r="D696" t="inlineStr"/>
       <c r="E696" t="inlineStr">
         <is>
           <t>至纯科技</t>
@@ -41034,7 +40308,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I696" t="inlineStr"/>
       <c r="J696" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41067,7 +40340,6 @@
           <t>人形机器人零部件</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
       <c r="E697" t="inlineStr">
         <is>
           <t>鸣志电器</t>
@@ -41088,7 +40360,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I697" t="inlineStr"/>
       <c r="J697" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41121,7 +40392,6 @@
           <t>光模块/CPO</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
       <c r="E698" t="inlineStr">
         <is>
           <t>剑桥科技</t>
@@ -41142,7 +40412,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I698" t="inlineStr"/>
       <c r="J698" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41237,7 +40506,6 @@
           <t>数控机床</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr"/>
       <c r="E700" t="inlineStr">
         <is>
           <t>科德数控</t>
@@ -41258,7 +40526,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I700" t="inlineStr"/>
       <c r="J700" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41291,7 +40558,6 @@
           <t>数控机床</t>
         </is>
       </c>
-      <c r="D701" t="inlineStr"/>
       <c r="E701" t="inlineStr">
         <is>
           <t>浙海德曼</t>
@@ -41312,7 +40578,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I701" t="inlineStr"/>
       <c r="J701" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41345,7 +40610,6 @@
           <t>精密零部件</t>
         </is>
       </c>
-      <c r="D702" t="inlineStr"/>
       <c r="E702" t="inlineStr">
         <is>
           <t>洁美科技</t>
@@ -41366,7 +40630,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I702" t="inlineStr"/>
       <c r="J702" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41399,7 +40662,6 @@
           <t>晶圆代工</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr">
         <is>
           <t>中芯集成</t>
@@ -41420,7 +40682,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I703" t="inlineStr"/>
       <c r="J703" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41453,7 +40714,6 @@
           <t>测量设备</t>
         </is>
       </c>
-      <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr">
         <is>
           <t>华峰测控</t>
@@ -41474,7 +40734,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I704" t="inlineStr"/>
       <c r="J704" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41507,7 +40766,6 @@
           <t>EDA/IP</t>
         </is>
       </c>
-      <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr">
         <is>
           <t>概伦电子</t>
@@ -41528,7 +40786,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I705" t="inlineStr"/>
       <c r="J705" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41561,7 +40818,6 @@
           <t>先进封装</t>
         </is>
       </c>
-      <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr">
         <is>
           <t>盛合晶微</t>
@@ -41582,7 +40838,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I706" t="inlineStr"/>
       <c r="J706" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41615,7 +40870,6 @@
           <t>网络/连接器</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
       <c r="E707" t="inlineStr">
         <is>
           <t>神宇股份</t>
@@ -41636,7 +40890,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I707" t="inlineStr"/>
       <c r="J707" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41669,7 +40922,6 @@
           <t>HBM产业链</t>
         </is>
       </c>
-      <c r="D708" t="inlineStr"/>
       <c r="E708" t="inlineStr">
         <is>
           <t>华海诚科</t>
@@ -41690,7 +40942,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I708" t="inlineStr"/>
       <c r="J708" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41748,7 +40999,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I709" t="inlineStr"/>
       <c r="J709" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41781,7 +41031,6 @@
           <t>人形机器人零部件</t>
         </is>
       </c>
-      <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr">
         <is>
           <t>步科股份</t>
@@ -41802,7 +41051,6 @@
           <t>stock_universe.yaml补入</t>
         </is>
       </c>
-      <c r="I710" t="inlineStr"/>
       <c r="J710" t="inlineStr">
         <is>
           <t>已纳入</t>
@@ -41937,7 +41185,6 @@
           <t>高</t>
         </is>
       </c>
-      <c r="L712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -41995,7 +41242,6 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -42563,22 +41809,22 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>AI算力与数据中心</t>
+          <t>先进封装与玻璃基板</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>AIDC供电/UPS/SST</t>
+          <t>CPO型槽/TGV激光加工</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>中压UPS/数据中心电源解决方案</t>
+          <t>参股烁光精密，超快激光微纳制造，40亿最小市值CPO+TGV标的</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>禾望电气</t>
+          <t>天安新材</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
@@ -42588,22 +41834,22 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>代表公司/公司类型</t>
+          <t>间接受益/参股</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>0701增补</t>
+          <t>0703材料新增</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>AI-2026-015</t>
+          <t>GLASS-2026-001</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>mapping</t>
+          <t>纳入</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
@@ -42613,7 +41859,7 @@
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>Meta中压UPS独供，Q3大批量订单落地，下一代UPS+SST方案</t>
+          <t>CPO型槽有国内头部客户订单，TGV下一阶段；603725</t>
         </is>
       </c>
     </row>
@@ -42625,22 +41871,22 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>国产算力与AI基础设施</t>
+          <t>半导体制造与材料</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>ASIC设计</t>
+          <t>存储设计/车载存储</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>ASIC平台/蜂窝基带IC</t>
+          <t>全球车规DRAM第四大供应商，26Q1利润+165%，AI服务器大厂转向车规压缩供给</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>翱捷科技</t>
+          <t>北京君正</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
@@ -42650,32 +41896,32 @@
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>代表公司/公司类型</t>
+          <t>核心受益</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>0701增补</t>
+          <t>0703材料新增</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>AI-2026-013</t>
+          <t>STORAGE-MEM-2026-001</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>mapping</t>
+          <t>纳入</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>云端推理ASIC+地平线机器人4nm芯片NRE，蜂窝业务扭亏</t>
+          <t>车载存储涨价超预期，26Q1毛利率43%；300223</t>
         </is>
       </c>
     </row>
@@ -42687,22 +41933,22 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>半导体制造与材料</t>
+          <t>AI电源与数据中心基础设施</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>半导体光刻材料</t>
+          <t>变压器出海/电力设备</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>空白掩膜板/光刻胶</t>
+          <t>收购烟台变压器厂100%股权，切入北美AIDC变压器短缺受益链</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>聚和材料</t>
+          <t>中际联合</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
@@ -42712,22 +41958,22 @@
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>代表公司/公司类型</t>
+          <t>新进入/跨界</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>0701增补</t>
+          <t>0703材料新增</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>SEMI-2026-005</t>
+          <t>TRANSFORMER-EXPORT-2026-001</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>mapping</t>
+          <t>纳入</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
@@ -42737,7 +41983,7 @@
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>并购SKE空白掩膜板（SK海力士核心供应商），DUV KrF/ArF PSM，光刻胶事业部建设中</t>
+          <t>原高空作业设备，跨界变压器，北美需求3-5年结构性短缺；605305</t>
         </is>
       </c>
     </row>
@@ -42749,22 +41995,22 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>半导体制造与材料</t>
+          <t>机器人与Physical AI</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>功率半导体</t>
+          <t>物理AI基础设施/仿真平台</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>功率分立器件+电源IC全栈IDM设计</t>
+          <t>投资上海松应科技2000万，成立风应科技，聚焦物理AI仿真训练基础设施</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>锴威特</t>
+          <t>风语筑</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
@@ -42774,32 +42020,32 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>代表公司/公司类型</t>
+          <t>早期信号/间接受益</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>0701增补</t>
+          <t>0703材料新增</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>SEMI-2026-010</t>
+          <t>ROBOT-2026-002</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>mapping</t>
+          <t>观察</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>国内少数同时自研功率分立+电源IC/BLDC驱动IDM，收购晶艺补齐高端电源IC，近四季度收入大幅增长</t>
+          <t>原文旅数字化，Physical AI是新方向，商业化待验证；603466</t>
         </is>
       </c>
     </row>
@@ -42811,57 +42057,1111 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
+          <t>AI电源与元器件</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>芯片电感/SST磁芯</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>与AI大客户芯片电感实质合作（750亿市值增量）+SST磁芯NDA签署（300亿），磁材绝对龙一</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>横店东磁</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>核心受益</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>0703材料新增</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>CAP-2026-001</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>芯片电感+SST磁芯双线，远期1500亿市值目标；002056</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
           <t>先进封装与玻璃基板</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr">
-        <is>
-          <t>先进封装材料/电镀</t>
-        </is>
-      </c>
-      <c r="D727" t="inlineStr">
-        <is>
-          <t>TGV光刻胶/先进封装电镀液</t>
-        </is>
-      </c>
-      <c r="E727" t="inlineStr">
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>PSPI材料</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>玻璃基板量产后用量提升近3倍，HBM+CoWoS+玻璃基板三线受益，京东方唯二供应商</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
         <is>
           <t>艾森股份</t>
         </is>
       </c>
-      <c r="F727" t="inlineStr">
+      <c r="F728" t="inlineStr">
         <is>
           <t>A股</t>
         </is>
       </c>
-      <c r="G727" t="inlineStr">
-        <is>
-          <t>代表公司/公司类型</t>
-        </is>
-      </c>
-      <c r="H727" t="inlineStr">
-        <is>
-          <t>0701增补</t>
-        </is>
-      </c>
-      <c r="I727" t="inlineStr">
-        <is>
-          <t>WAFER-2026-001</t>
-        </is>
-      </c>
-      <c r="J727" t="inlineStr">
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>核心受益</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>0703材料新增</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>GLASS-2026-001</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>单线价值量是PCB几十倍，玻璃基板量产的直接材料受益；688720</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>服务器/超节点整机</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>服务器ODM/昇腾整机</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>神州数码</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>AI-2026-016</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
         <is>
           <t>mapping</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="L727" t="inlineStr">
-        <is>
-          <t>长鑫HBM封装胶baseline，TGV光刻胶+先进封装电镀液，HBM封装需求放量受益</t>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>昇腾整机/算力一体机，直接承接超节点放量</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>服务器/超节点整机</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>昇腾算力一体机</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>恒为科技</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>A股/科创板</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>AI-2026-016</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>昇腾超节点整机核心标的</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>服务器/超节点整机</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>昇腾算力一体机</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>拓维信息</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>AI-2026-016</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>昇腾算力整机，直接承接超节点放量</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>ASIC定制芯片</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>ASIC设计/蜂窝+机器人</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>翱捷科技</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>A股/科创板</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>AI-2026-018</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>地平线机器人ASIC项目（4nm，400-500美金/颗）；单颗NRE约2亿；蜂窝基带业务400亿安全底</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>ASIC定制芯片</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>ASIC设计服务/IP授权</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>灿芯股份</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>A股/科创板</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>AI-2026-018</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>中芯国际第一大股东；阿里临港300亿投入先遣2亿订单；类比台湾世芯之于亚马逊/谷歌</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>算力租赁</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>大模型算力服务商</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>行云科技</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>非上市/未知</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>间接受益</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>AI-RENT-2026-001</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>待核验</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>智谱框架协议约55亿，B300已交付；若上市则为算力租赁核心标的</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>数据中心设备</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>AI服务器线束盒</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>恒林股份</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>AI-2026-016</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>子公司太仓吉盟，英伟达线束盒供应链占比超70%；液冷柜新品类下半年放量</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>数据中心制冷</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>磁悬浮冷水机组</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>磁谷科技</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>A股/创业板</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>AI-2026-011</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>磁悬浮冷水机组，东南亚数据中心合资（与EPG持股70%），北美供需缺口明确；比泽尔合资压缩机</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>AI光通信与高速互联</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>MPO连接器</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>MPO直供谷歌</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>汇聚科技</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>AI-2026-011</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>直供谷歌MPO，H1超去年全年；立讯背景，中长期收并购预期；半年目标600亿市值</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>AI光通信与高速互联</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>MPO连接器</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>MPO A股基本面最硬</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>长芯博创</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>AI-2026-011</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>长飞+谷歌背景，A股MPO基本面最硬；2H剩余股权收购+AOC放量催化；目标1500亿市值</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>CDN/边缘计算</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>CDN服务</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>CDN国内龙头</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>网宿科技</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>A股/创业板</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>SIG-20260708-004</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>国内独立CDN绝对龙头，2月已率先涨价35-40%；Akamai退出后承接高端客户；CDN及边缘计算占收入62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>CDN/边缘计算</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>CDN服务</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>专精特新CDN黑马</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>南兴股份</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>SIG-20260708-004</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>子公司唯一网络自研CDN平台；华为云核心供应商；IDC及云服务占总收入45%；45亿市值估值历史底部</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>CDN/边缘计算</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>CDN服务</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>CDN小市值弹性</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>二六三</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>间接受益</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>SIG-20260708-004</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>子公司推云科技纯CDN，面向中小企业及跨境；总市值约70亿，CDN涨价中边际弹性可观</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>CDN/边缘计算</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>CDN服务</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>CDN+安全一体化</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>深信服</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>直接受益</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>SIG-20260708-004</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>CDN+网络安全，AI推理分发受益标的</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>半导体材料</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>湿化学品/刻蚀液</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>翰博高新</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>间接受益</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>SEMI-2026-014</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>参股公司芯东进收购韩国东进在华湿化学品资产（7月7日完成），切入刻蚀液/剥离液赛道；远期10x空间</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>AI NAS/端侧算力</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>PC ODM/AI NAS工作站</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>亿道信息</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>间接受益</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>0708批次</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>AI-2026-018</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>AI NAS个人工作站产品与大厂合作；主业PC/工作站ODM；Q1收入11.3亿+107%；存储涨价受益</t>
         </is>
       </c>
     </row>

--- a/data/company-pool/公司.xlsx
+++ b/data/company-pool/公司.xlsx
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L744"/>
+  <dimension ref="A1:L762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>POWER-DC-2026-002</t>
+          <t>POWER-DC-2026-003;POWER-DC-2026-002</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>HW950-2026-001;SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -19975,7 +19975,7 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>SPACE-2026-001</t>
+          <t>SPACE-2026-002;SPACE-2026-001</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>SPACE-2026-001</t>
+          <t>SPACE-2026-002;SPACE-2026-001</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>SPACE-2026-001</t>
+          <t>SPACE-2026-002;SPACE-2026-001</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>SPACE-2026-001</t>
+          <t>SPACE-2026-002;SPACE-2026-001</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>SPACE-2026-001</t>
+          <t>SPACE-2026-002;SPACE-2026-001</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
@@ -23172,7 +23172,7 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>AI-2026-012</t>
+          <t>STORAGE-MEM-2026-001;AI-2026-012</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
@@ -37992,7 +37992,7 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>MLCC-2026-001</t>
+          <t>STORAGE-MEM-2026-001;MLCC-2026-001</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
@@ -38049,7 +38049,7 @@
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>MLCC-2026-001</t>
+          <t>STORAGE-MEM-2026-001;MLCC-2026-001</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
@@ -38220,7 +38220,7 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>MLCC-2026-001</t>
+          <t>STORAGE-MEM-2026-001;MLCC-2026-001</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
@@ -41844,7 +41844,7 @@
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>GLASS-2026-001</t>
+          <t>NPO-2026-001;GLASS-2026-001</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
@@ -43162,6 +43162,1032 @@
       <c r="L744" t="inlineStr">
         <is>
           <t>AI NAS个人工作站产品与大厂合作；主业PC/工作站ODM；Q1收入11.3亿+107%；存储涨价受益</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>光通信与高速连接</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>光纤预制棒/光棒</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>光纤预制棒(全合成工艺)、光棒-光纤-光缆一体化</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>领益智造</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>0710公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>FIBER-2026-002</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>洁净室工程</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>洁净室工程设计施工、AIDC/晶圆厂配套工程</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>亚翔集成</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>CLEANROOM-2026-001</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>洁净室工程</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>洁净室工程设计施工、AIDC/晶圆厂配套工程</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>圣晖集成</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>CLEANROOM-2026-001</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>洁净室工程</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>洁净室工程设计施工、AIDC/晶圆厂配套工程</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>柏诚股份</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>CLEANROOM-2026-001</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>洁净室工程</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>洁净室工程设计施工、AIDC/晶圆厂配套工程</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>深桑达A</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>CLEANROOM-2026-001</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>洁净室工程</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>洁净室工程设计施工、AIDC/晶圆厂配套工程</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>华康洁净</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>CLEANROOM-2026-001</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>洁净室工程</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>洁净室工程设计施工、AIDC/晶圆厂配套工程</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>太极实业</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>CLEANROOM-2026-001</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>海上回收保障、火箭结构材料、卫星载荷</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>海上回收平台/打捞、火箭结构件与耗材、卫星电源/载荷芯片</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>巨力索具</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>SPACE-2026-002</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>海上回收保障、火箭结构材料、卫星载荷</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>海上回收平台/打捞、火箭结构件与耗材、卫星电源/载荷芯片</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>海兰信</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>SPACE-2026-002</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>海上回收保障、火箭结构材料、卫星载荷</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>海上回收平台/打捞、火箭结构件与耗材、卫星电源/载荷芯片</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>斯瑞新材</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>SPACE-2026-002</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>海上回收保障、火箭结构材料、卫星载荷</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>海上回收平台/打捞、火箭结构件与耗材、卫星电源/载荷芯片</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>ST臻镭</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>SPACE-2026-002</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>海上回收保障、火箭结构材料、卫星载荷</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>海上回收平台/打捞、火箭结构件与耗材、卫星电源/载荷芯片</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>铖昌科技</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>SPACE-2026-002</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>散热/热管理</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>关节/电池包/计算单元系统级液冷散热模组</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>东方电热</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>ROBOT-2026-002</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>散热/热管理</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>关节/电池包/计算单元系统级液冷散热模组</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>中鼎股份</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>ROBOT-2026-002</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>综合电子元器件分销</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>存储芯片、功率器件、MLCC、钽电容分销渠道</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>雅创电子</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>STORAGE-MEM-2026-001</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>综合电子元器件分销</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>存储芯片、功率器件、MLCC、钽电容分销渠道</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>STORAGE-MEM-2026-001</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>综合电子元器件分销</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>存储芯片、功率器件、MLCC、钽电容分销渠道</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>利尔达</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>STORAGE-MEM-2026-001</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>存储</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>综合电子元器件分销</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>存储芯片、功率器件、MLCC、钽电容分销渠道</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>好上好</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>A股</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>代表公司/公司类型</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>0711公司池自动同步</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>STORAGE-MEM-2026-001</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>mapping自动同步</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
     </row>
@@ -65513,7 +66539,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -65684,7 +66710,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -65741,7 +66767,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -65798,7 +66824,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -65855,7 +66881,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -65912,7 +66938,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>GLASS-2026-001 / PACKAGING</t>
+          <t>HW950-2026-001;SEMI-2026-012;GLASS-2026-001 / PACKAGING</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
